--- a/events/Tacen_2022_WC/Tacen_2022_WC_start.xlsx
+++ b/events/Tacen_2022_WC/Tacen_2022_WC_start.xlsx
@@ -33250,6 +33250,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X562" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -34129,6 +34134,11 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
+      <c r="X575" t="inlineStr">
+        <is>
+          <t>37267</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -36912,6 +36922,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X616" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -37519,6 +37534,11 @@
           <t>VALIKOVA Barbora</t>
         </is>
       </c>
+      <c r="X625" t="inlineStr">
+        <is>
+          <t>37267</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -38942,6 +38962,11 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
+      <c r="X646" t="inlineStr">
+        <is>
+          <t>42016</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -39897,6 +39922,11 @@
       <c r="R660" t="inlineStr">
         <is>
           <t>FISEROVA Tereza</t>
+        </is>
+      </c>
+      <c r="X660" t="inlineStr">
+        <is>
+          <t>42016</t>
         </is>
       </c>
     </row>
